--- a/data/GPS/Metricas_GPS7.xlsx
+++ b/data/GPS/Metricas_GPS7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30506"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2070CB3775220E96AE6CCF3ADD1E570FE97B8056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2070CB3775220E96AE6CCF3ADD1E570FE97B8056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3C6B377-A672-42BE-8B03-D4E395CFE89B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>Fecha</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>Delantero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Garcia_Gumiel </t>
   </si>
 </sst>
 </file>
@@ -443,7 +440,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="22.21875" customWidth="1"/>
@@ -1154,53 +1151,6 @@
         <v>936.08</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>46256</v>
-      </c>
-      <c r="B16" s="1">
-        <v>146.88300000000001</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="1">
-        <v>6.05</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="G16" s="1">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>2</v>
-      </c>
-      <c r="J16" s="1">
-        <v>27</v>
-      </c>
-      <c r="K16" s="1">
-        <v>25</v>
-      </c>
-      <c r="L16" s="1">
-        <v>4.2779999999999996</v>
-      </c>
-      <c r="M16" s="1">
-        <v>-5.2160000000000002</v>
-      </c>
-      <c r="N16" s="1">
-        <v>25.908999999999999</v>
-      </c>
-      <c r="O16" s="1">
-        <v>1078.9349999999999</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
